--- a/wiki/reports/daily/2026-09-17_일일보고.xlsx
+++ b/wiki/reports/daily/2026-09-17_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,13 +75,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -96,11 +91,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,22 +182,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,22 +215,13 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -623,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-09-17 07:57   |   전일: 9월 16일   |   월평균 기준: 이전 작업일 12일 평균   |   9월 누적 작업일: 13일</t>
+          <t>생성: 2026-09-17 16:00   |   전일: 9월 16일   |   월평균 기준: 이전 작업일 12일 평균   |   9월 누적 작업일: 13일</t>
         </is>
       </c>
     </row>
@@ -685,25 +675,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>16</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-6</v>
+        <v>30</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.375</v>
+        <v>1.875</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>29.2</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-19.16666666666667</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.6571428571428571</v>
+        <v>0.5771428571428571</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -714,205 +704,205 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4930</v>
+        <v>19042</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>4081</v>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>849</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>0.2080372457730948</v>
+      <c r="D5" s="7" t="n">
+        <v>14961</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>3.666013232050968</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>7052.4</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-2122.416666666667</v>
+        <v>11989.58333333333</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.3009488473218401</v>
+        <v>1.700067352798686</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>1:22:10</t>
+          <t>5:17:22</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>GX7  수량 (개)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-15</v>
+        <v>25</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-14.75</v>
+        <v>25.25</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-1</v>
+        <v>1.711864406779661</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>GX7  가공시간 (초)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>13790</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>5007</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-5007</v>
+        <v>8783</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-1</v>
+        <v>1.754144198122628</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>5403.5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-5403.5</v>
+        <v>8386.5</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-1</v>
+        <v>1.552049597483113</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>3:49:50</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>31</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-21</v>
+        <v>55</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.6774193548387096</v>
+        <v>1.774193548387097</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>43.9</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-33.91666666666666</v>
+        <v>42.08333333333334</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.7722960151802657</v>
+        <v>0.9582542694497155</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>4930</v>
+        <v>32832</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>9088</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-4158</v>
+        <v>23744</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.4575264084507042</v>
+        <v>2.612676056338028</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>12455.9</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-7525.916666666666</v>
+        <v>20376.08333333334</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.6042041600042818</v>
+        <v>1.635855784734163</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>1:22:10</t>
+          <t>9:07:12</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>31</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-21</v>
+        <v>55</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.6774193548387096</v>
+        <v>1.774193548387097</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>42.8</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-32.83333333333334</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.7665369649805448</v>
+        <v>1.007782101167315</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>9월 누적  (13일 / 17일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="n">
-        <v>537</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>154401</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>524</v>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n">
+        <v>613</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>182303</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -930,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -954,213 +944,354 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="18" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>R0.5</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>0303</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr"/>
-      <c r="I4" s="21" t="n">
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="19" t="n">
         <v>4930</v>
       </c>
-      <c r="K4" s="19" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>1:22:10</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>14112</v>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>3:55:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="16" t="n">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>19042</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>5:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>■ GX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>형상</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>날수(F)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>날경(Ø)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>상크경(Ø)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>코팅</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>수량(개)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>시간합계(초)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>시간(H:M:S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="16" t="n">
-        <v>4930</v>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>1:22:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>■ GX7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>형상</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>날수(F)</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>날경(Ø)</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>코팅</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>시간합계(초)</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr">
-        <is>
-          <t>시간(H:M:S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
+      <c r="E10" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr"/>
+      <c r="I10" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>8640</v>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>2:24:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr"/>
+      <c r="I11" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>5150</v>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>1:25:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>GX7 소계</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>13790</v>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>3:49:50</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
